--- a/simulations/AON_84/economics_AON_84.xlsx
+++ b/simulations/AON_84/economics_AON_84.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AON_84\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99AA4F3-43E1-432C-976E-0B8CC67B89FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F8CB8E-9FA1-4D92-863F-914238F25D25}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPEX" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="134">
   <si>
     <t>Cost factors</t>
   </si>
@@ -395,9 +395,6 @@
     <t>Working capital</t>
   </si>
   <si>
-    <t>Purchased equipment cost 2019 (M$/year)</t>
-  </si>
-  <si>
     <t>Supervision</t>
   </si>
   <si>
@@ -470,9 +467,6 @@
     <t>Reference Data</t>
   </si>
   <si>
-    <t>2019 costs</t>
-  </si>
-  <si>
     <t xml:space="preserve">OPEX (M$/year) </t>
   </si>
   <si>
@@ -509,9 +503,6 @@
     <t>Fixed production costs (M$/year)</t>
   </si>
   <si>
-    <t>Fossil ammonia 2019</t>
-  </si>
-  <si>
     <t>Fossil ammonia 2022</t>
   </si>
   <si>
@@ -533,9 +524,6 @@
     <t>Utility costs</t>
   </si>
   <si>
-    <t>Price 2019 ($/unit)</t>
-  </si>
-  <si>
     <t>Price 2022 ($/unit)</t>
   </si>
   <si>
@@ -545,9 +533,6 @@
     <t>OPEX (wind ammonia)</t>
   </si>
   <si>
-    <t>Wind ammonia 2019</t>
-  </si>
-  <si>
     <t>Wind ammonia 2022</t>
   </si>
   <si>
@@ -575,7 +560,55 @@
     <t>E-103</t>
   </si>
   <si>
-    <t>Natural gas</t>
+    <t>E-104</t>
+  </si>
+  <si>
+    <t>E-105</t>
+  </si>
+  <si>
+    <t>E-106</t>
+  </si>
+  <si>
+    <t>E-107</t>
+  </si>
+  <si>
+    <t>E-108</t>
+  </si>
+  <si>
+    <t>E-109</t>
+  </si>
+  <si>
+    <t>E-110</t>
+  </si>
+  <si>
+    <t>E-111</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Pressure Vessel</t>
+  </si>
+  <si>
+    <t>Valve trays</t>
+  </si>
+  <si>
+    <t>Tray</t>
+  </si>
+  <si>
+    <t>diameter, m</t>
+  </si>
+  <si>
+    <t>B11 distillation column</t>
+  </si>
+  <si>
+    <t>N stages</t>
+  </si>
+  <si>
+    <t>Refrigerant to -175 °C</t>
   </si>
 </sst>
 </file>
@@ -832,9 +865,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -843,6 +873,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -864,20 +900,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -1161,7 +1189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q102"/>
+  <dimension ref="A1:T111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
@@ -1174,22 +1202,24 @@
     <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
-    <row r="2" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1200,7 +1230,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1211,7 +1241,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1222,7 +1252,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -1233,7 +1263,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -1244,7 +1274,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -1255,7 +1285,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -1266,7 +1296,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -1277,12 +1307,12 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
     </row>
-    <row r="12" spans="1:17" ht="63.75" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="63.75" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>9</v>
       </c>
@@ -1307,84 +1337,88 @@
       <c r="H12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="M12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L12" s="5" t="s">
+      <c r="N12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="O12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="N12" s="5" t="s">
+      <c r="P12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="O12" s="5" t="s">
+      <c r="Q12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="P12" s="5" t="s">
+      <c r="R12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Q12" s="5" t="s">
+      <c r="S12" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="48" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="50"/>
-      <c r="J13" s="33" t="s">
+      <c r="T12" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="51"/>
+      <c r="L13" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="K13" s="34">
+      <c r="M13" s="34">
         <v>1.8288</v>
       </c>
-      <c r="L13" s="34">
-        <f>4.572+2*0.25*K13</f>
+      <c r="N13" s="34">
+        <f>4.572+2*0.25*M13</f>
         <v>5.4863999999999997</v>
       </c>
-      <c r="M13" s="37">
-        <f t="shared" ref="M13" si="0">K13+0.0254</f>
+      <c r="O13" s="37">
+        <f t="shared" ref="O13" si="0">M13+0.0254</f>
         <v>1.8542000000000001</v>
       </c>
-      <c r="N13" s="37">
-        <f t="shared" ref="N13" si="1">PI()*(M13*M13-K13*K13)/4</f>
+      <c r="P13" s="37">
+        <f t="shared" ref="P13" si="1">PI()*(O13*O13-M13*M13)/4</f>
         <v>7.3472584469137403E-2</v>
       </c>
-      <c r="O13" s="37">
-        <f t="shared" ref="O13" si="2">N13*L13</f>
+      <c r="Q13" s="37">
+        <f t="shared" ref="Q13" si="2">P13*N13</f>
         <v>0.4030999874314754</v>
       </c>
-      <c r="P13" s="35">
+      <c r="R13" s="35">
         <v>8000</v>
       </c>
-      <c r="Q13" s="34">
-        <f t="shared" ref="Q13" si="3">P13*O13</f>
+      <c r="S13" s="34">
+        <f t="shared" ref="S13" si="3">R13*Q13</f>
         <v>3224.7998994518034</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="T13" s="6"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D14" s="9">
-        <v>1791.396</v>
+        <v>1791.4096500000001</v>
       </c>
       <c r="E14" s="8">
         <v>580000</v>
@@ -1397,50 +1431,51 @@
       </c>
       <c r="H14" s="9">
         <f t="shared" ref="H14" si="4">(E14+(F14*(D14^G14)))/1000000</f>
-        <v>2.3703789197489726</v>
-      </c>
-      <c r="J14" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="K14" s="34">
-        <v>1.8288</v>
-      </c>
-      <c r="L14" s="34">
-        <f>3.6576+2*0.25*K14</f>
-        <v>4.5720000000000001</v>
-      </c>
-      <c r="M14" s="37">
-        <f t="shared" ref="M14" si="5">K14+0.0254</f>
-        <v>1.8542000000000001</v>
-      </c>
-      <c r="N14" s="37">
-        <f t="shared" ref="N14" si="6">PI()*(M14*M14-K14*K14)/4</f>
-        <v>7.3472584469137403E-2</v>
+        <v>2.3703871050865568</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="M14" s="34">
+        <v>1.524</v>
+      </c>
+      <c r="N14" s="34">
+        <f>3.6576+2*0.25*M14</f>
+        <v>4.4196</v>
       </c>
       <c r="O14" s="37">
-        <f t="shared" ref="O14" si="7">N14*L14</f>
-        <v>0.33591665619289623</v>
-      </c>
-      <c r="P14" s="35">
+        <f t="shared" ref="O14" si="5">M14+0.0254</f>
+        <v>1.5494000000000001</v>
+      </c>
+      <c r="P14" s="37">
+        <f t="shared" ref="P14" si="6">PI()*(O14*O14-M14*M14)/4</f>
+        <v>6.1311604970797184E-2</v>
+      </c>
+      <c r="Q14" s="37">
+        <f t="shared" ref="Q14" si="7">P14*N14</f>
+        <v>0.27097276932893521</v>
+      </c>
+      <c r="R14" s="35">
         <v>8000</v>
       </c>
-      <c r="Q14" s="34">
-        <f t="shared" ref="Q14" si="8">P14*O14</f>
-        <v>2687.33324954317</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="S14" s="34">
+        <f t="shared" ref="S14" si="8">R14*Q14</f>
+        <v>2167.7821546314817</v>
+      </c>
+      <c r="T14" s="6"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D15" s="9">
-        <v>676.195155</v>
+        <v>676.20022900000004</v>
       </c>
       <c r="E15" s="8">
         <v>580000</v>
@@ -1453,53 +1488,86 @@
       </c>
       <c r="H15" s="9">
         <f t="shared" ref="H15" si="9">(E15+(F15*(D15^G15)))/1000000</f>
-        <v>1.5778683049926348</v>
-      </c>
-      <c r="J15" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="K15" s="34">
+        <v>1.5778727976390048</v>
+      </c>
+      <c r="L15" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" s="34">
         <v>1.8288</v>
       </c>
-      <c r="L15" s="34">
-        <f>4.572+2*0.25*K15</f>
+      <c r="N15" s="34">
+        <f>4.572+2*0.25*M15</f>
         <v>5.4863999999999997</v>
       </c>
-      <c r="M15" s="37">
-        <f t="shared" ref="M15" si="10">K15+0.0254</f>
+      <c r="O15" s="37">
+        <f t="shared" ref="O15:O16" si="10">M15+0.0254</f>
         <v>1.8542000000000001</v>
       </c>
-      <c r="N15" s="37">
-        <f t="shared" ref="N15" si="11">PI()*(M15*M15-K15*K15)/4</f>
+      <c r="P15" s="37">
+        <f t="shared" ref="P15:P16" si="11">PI()*(O15*O15-M15*M15)/4</f>
         <v>7.3472584469137403E-2</v>
       </c>
-      <c r="O15" s="37">
-        <f t="shared" ref="O15" si="12">N15*L15</f>
+      <c r="Q15" s="37">
+        <f t="shared" ref="Q15:Q16" si="12">P15*N15</f>
         <v>0.4030999874314754</v>
       </c>
-      <c r="P15" s="35">
+      <c r="R15" s="35">
         <v>8000</v>
       </c>
-      <c r="Q15" s="34">
-        <f t="shared" ref="Q15" si="13">P15*O15</f>
+      <c r="S15" s="34">
+        <f t="shared" ref="S15:S16" si="13">R15*Q15</f>
         <v>3224.7998994518034</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="48" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="50"/>
+      <c r="T15" s="6"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="51"/>
+      <c r="L16" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="M16" s="34">
+        <v>1.3040656989999999</v>
+      </c>
+      <c r="N16" s="34">
+        <f>0.6096*7</f>
+        <v>4.2671999999999999</v>
+      </c>
+      <c r="O16" s="37">
+        <f t="shared" si="10"/>
+        <v>1.329465699</v>
+      </c>
+      <c r="P16" s="37">
+        <f t="shared" si="11"/>
+        <v>5.2536616370263509E-2</v>
+      </c>
+      <c r="Q16" s="37">
+        <f t="shared" si="12"/>
+        <v>0.22418424937518844</v>
+      </c>
+      <c r="R16" s="35">
+        <v>8000</v>
+      </c>
+      <c r="S16" s="34">
+        <f t="shared" si="13"/>
+        <v>1793.4739950015075</v>
+      </c>
+      <c r="T16" s="47">
+        <v>7</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>49</v>
@@ -1509,7 +1577,7 @@
       </c>
       <c r="D17" s="21">
         <f>I17/J17</f>
-        <v>491.75465533268437</v>
+        <v>400.80804967372302</v>
       </c>
       <c r="E17" s="8">
         <v>28000</v>
@@ -1522,18 +1590,18 @@
       </c>
       <c r="H17" s="9">
         <f>(E17+(F17*(D17^G17)))/1000000*J17</f>
-        <v>1.915614244965248</v>
-      </c>
-      <c r="I17" s="46">
-        <v>7868.0744853229498</v>
-      </c>
-      <c r="J17" s="47">
-        <v>16</v>
+        <v>0.99765791992941399</v>
+      </c>
+      <c r="I17" s="45">
+        <v>4008.0804967372301</v>
+      </c>
+      <c r="J17" s="46">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>49</v>
@@ -1542,8 +1610,8 @@
         <v>50</v>
       </c>
       <c r="D18" s="21">
-        <f>I18/J18</f>
-        <v>393.07391987367549</v>
+        <f t="shared" ref="D18:D25" si="14">I18/J18</f>
+        <v>71.255186199285603</v>
       </c>
       <c r="E18" s="8">
         <v>28000</v>
@@ -1555,19 +1623,19 @@
         <v>1.2</v>
       </c>
       <c r="H18" s="9">
-        <f>(E18+(F18*(D18^G18)))/1000000*J18</f>
-        <v>0.19621446883953406</v>
-      </c>
-      <c r="I18" s="46">
-        <v>786.14783974735099</v>
-      </c>
-      <c r="J18" s="47">
-        <v>2</v>
+        <f t="shared" ref="H18:H25" si="15">(E18+(F18*(D18^G18)))/1000000*J18</f>
+        <v>3.7031783840171473E-2</v>
+      </c>
+      <c r="I18" s="45">
+        <v>71.255186199285603</v>
+      </c>
+      <c r="J18" s="46">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>49</v>
@@ -1576,8 +1644,8 @@
         <v>50</v>
       </c>
       <c r="D19" s="21">
-        <f>I19/J19</f>
-        <v>412.21844867378206</v>
+        <f t="shared" si="14"/>
+        <v>91.189690305731702</v>
       </c>
       <c r="E19" s="8">
         <v>28000</v>
@@ -1589,372 +1657,607 @@
         <v>1.2</v>
       </c>
       <c r="H19" s="9">
-        <f>(E19+(F19*(D19^G19)))/1000000*J19</f>
-        <v>1.0222439549977951</v>
-      </c>
-      <c r="I19" s="46">
-        <v>4122.1844867378204</v>
-      </c>
-      <c r="J19" s="47">
-        <v>10</v>
+        <f t="shared" si="15"/>
+        <v>4.0143074199624804E-2</v>
+      </c>
+      <c r="I19" s="45">
+        <v>91.189690305731702</v>
+      </c>
+      <c r="J19" s="46">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="53"/>
+      <c r="A20" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="21">
+        <f t="shared" si="14"/>
+        <v>166.93332592918799</v>
+      </c>
+      <c r="E20" s="8">
+        <v>28000</v>
+      </c>
+      <c r="F20" s="8">
+        <v>54</v>
+      </c>
+      <c r="G20" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="H20" s="9">
+        <f t="shared" si="15"/>
+        <v>5.3086808537225354E-2</v>
+      </c>
+      <c r="I20" s="45">
+        <v>166.93332592918799</v>
+      </c>
+      <c r="J20" s="46">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>91</v>
+      <c r="A21" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="9">
-        <f>Q15</f>
-        <v>3224.7998994518034</v>
+        <v>50</v>
+      </c>
+      <c r="D21" s="21">
+        <f t="shared" si="14"/>
+        <v>17.178391507646801</v>
       </c>
       <c r="E21" s="8">
-        <v>17400</v>
+        <v>28000</v>
       </c>
       <c r="F21" s="8">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="G21" s="9">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="H21" s="9">
-        <f>(E21+(F21*(D21^G21)))/1000000</f>
-        <v>9.3232338201156256E-2</v>
+        <f t="shared" si="15"/>
+        <v>2.9638222006174931E-2</v>
+      </c>
+      <c r="I21" s="45">
+        <v>17.178391507646801</v>
+      </c>
+      <c r="J21" s="46">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="48" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="50"/>
+      <c r="A22" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="21">
+        <f t="shared" si="14"/>
+        <v>481.83532004832597</v>
+      </c>
+      <c r="E22" s="8">
+        <v>28000</v>
+      </c>
+      <c r="F22" s="8">
+        <v>54</v>
+      </c>
+      <c r="G22" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="H22" s="9">
+        <f t="shared" si="15"/>
+        <v>0.5875505782011079</v>
+      </c>
+      <c r="I22" s="45">
+        <v>2409.1766002416298</v>
+      </c>
+      <c r="J22" s="46">
+        <v>5</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="9">
-        <f>Q13</f>
-        <v>3224.7998994518034</v>
+        <v>50</v>
+      </c>
+      <c r="D23" s="21">
+        <f t="shared" si="14"/>
+        <v>129.38827884954</v>
       </c>
       <c r="E23" s="8">
-        <v>17400</v>
+        <v>28000</v>
       </c>
       <c r="F23" s="8">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="G23" s="9">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="H23" s="9">
-        <f>(E23+(F23*(D23^G23)))/1000000</f>
-        <v>9.3232338201156256E-2</v>
+        <f t="shared" si="15"/>
+        <v>4.6478541209650948E-2</v>
+      </c>
+      <c r="I23" s="45">
+        <v>129.38827884954</v>
+      </c>
+      <c r="J23" s="46">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="21">
+        <f t="shared" si="14"/>
+        <v>66.820114482875496</v>
+      </c>
+      <c r="E24" s="8">
+        <v>28000</v>
+      </c>
+      <c r="F24" s="8">
+        <v>54</v>
+      </c>
+      <c r="G24" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="H24" s="9">
+        <f t="shared" si="15"/>
+        <v>3.6361465810052861E-2</v>
+      </c>
+      <c r="I24" s="45">
+        <v>66.820114482875496</v>
+      </c>
+      <c r="J24" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="21">
+        <f t="shared" si="14"/>
+        <v>2.4937227319470798</v>
+      </c>
+      <c r="E25" s="8">
+        <v>28000</v>
+      </c>
+      <c r="F25" s="8">
+        <v>54</v>
+      </c>
+      <c r="G25" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="H25" s="9">
+        <f t="shared" si="15"/>
+        <v>2.8161663343600665E-2</v>
+      </c>
+      <c r="I25" s="45">
+        <v>2.4937227319470798</v>
+      </c>
+      <c r="J25" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="54"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="9">
+        <f>S15</f>
+        <v>3224.7998994518034</v>
+      </c>
+      <c r="E27" s="8">
+        <v>17400</v>
+      </c>
+      <c r="F27" s="8">
+        <v>79</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="H27" s="9">
+        <f>(E27+(F27*(D27^G27)))/1000000</f>
+        <v>9.3232338201156256E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="51"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="9">
+        <f>S16</f>
+        <v>1793.4739950015075</v>
+      </c>
+      <c r="E29" s="8">
+        <v>17400</v>
+      </c>
+      <c r="F29" s="8">
+        <v>79</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="H29" s="9">
+        <f t="shared" ref="H29" si="16">(E29+(F29*(D29^G29)))/1000000</f>
+        <v>6.3454058955732251E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30" s="9">
+        <f>M16</f>
+        <v>1.3040656989999999</v>
+      </c>
+      <c r="E30" s="8">
+        <v>210</v>
+      </c>
+      <c r="F30" s="8">
+        <v>400</v>
+      </c>
+      <c r="G30" s="9">
+        <v>1.9</v>
+      </c>
+      <c r="H30" s="9">
+        <f>(E30+(F30*(D30^G30)))*T16/1000000</f>
+        <v>6.1068925020898463E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="51"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="9">
-        <f>Q14</f>
-        <v>2687.33324954317</v>
-      </c>
-      <c r="E24" s="8">
+      <c r="D32" s="9">
+        <f>S13</f>
+        <v>3224.7998994518034</v>
+      </c>
+      <c r="E32" s="8">
         <v>17400</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F32" s="8">
         <v>79</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G32" s="9">
         <v>0.85</v>
       </c>
-      <c r="H24" s="9">
-        <f t="shared" ref="H24" si="14">(E24+(F24*(D24^G24)))/1000000</f>
-        <v>8.2345697894963321E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H25" s="38">
-        <f>SUM(H14:H24)</f>
-        <v>7.3511302678414605</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
+      <c r="H32" s="9">
+        <f>(E32+(F32*(D32^G32)))/1000000</f>
+        <v>9.3232338201156256E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="9">
+        <f>S14</f>
+        <v>2167.7821546314817</v>
+      </c>
+      <c r="E33" s="8">
+        <v>17400</v>
+      </c>
+      <c r="F33" s="8">
+        <v>79</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0.85</v>
+      </c>
+      <c r="H33" s="9">
+        <f t="shared" ref="H33" si="17">(E33+(F33*(D33^G33)))/1000000</f>
+        <v>7.1505371404593496E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H34" s="38">
+        <f>SUM(H14:H33)</f>
+        <v>6.1319009590673117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="21">
+      <c r="B35" s="21">
         <v>532.9</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="21">
+      <c r="B36" s="21">
         <v>607.5</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B28" s="21">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="21">
         <v>816</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="21">
-        <f>H25*B27/B26</f>
-        <v>8.3802057378751886</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="B30" s="21">
-        <f>H25*B28/B26</f>
-        <v>11.256375114578029</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="39"/>
-      <c r="B31" s="32"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="36">
-        <v>2019</v>
-      </c>
-      <c r="C32" s="36">
+      <c r="B38" s="21">
+        <f>H34*B36/B35</f>
+        <v>6.9902980533559615</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="21">
+        <f>H34*B37/B35</f>
+        <v>9.3894373852485007</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" s="39"/>
+      <c r="B40" s="32"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B41" s="36">
         <v>2022</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="26" t="s">
+      <c r="C41" s="31"/>
+      <c r="D41"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="40">
-        <f>(B29)*((1+C3)+(C2+C5+C4+C6+C7+C8)/C9)*C9</f>
-        <v>31.341969459653214</v>
-      </c>
-      <c r="C33" s="40">
-        <f>(B30)*((1+C3)+(C2+C5+C4+C6+C7+C8)/C9)*C9</f>
-        <v>42.098842928521833</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="26" t="s">
+      <c r="B42" s="40">
+        <f>(B39)*((1+C3)+(C2+C5+C4+C6+C7+C8)/C9)*C9</f>
+        <v>35.1164958208294</v>
+      </c>
+      <c r="C42" s="31"/>
+      <c r="D42"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B34" s="40">
-        <f>0.3*B33</f>
-        <v>9.4025908378959642</v>
-      </c>
-      <c r="C34" s="40">
-        <f>0.3*C33</f>
-        <v>12.62965287855655</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
+      <c r="B43" s="40">
+        <f>0.3*B42</f>
+        <v>10.534948746248819</v>
+      </c>
+      <c r="C43" s="31"/>
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="40">
-        <f>0.3*SUM(B33:B34)</f>
-        <v>12.223368089264753</v>
-      </c>
-      <c r="C35" s="40">
-        <f>0.3*SUM(C33:C34)</f>
-        <v>16.418548742123512</v>
-      </c>
-      <c r="D35"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="26" t="s">
+      <c r="B44" s="40">
+        <f>0.3*SUM(B42:B43)</f>
+        <v>13.695433370123464</v>
+      </c>
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="40">
-        <f>0.1*SUM(B33:B34)</f>
-        <v>4.0744560297549182</v>
-      </c>
-      <c r="C36" s="40">
-        <f>0.1*SUM(C33:C34)</f>
-        <v>5.4728495807078383</v>
-      </c>
-      <c r="D36"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="26" t="s">
+      <c r="B45" s="40">
+        <f>0.1*SUM(B42:B43)</f>
+        <v>4.5651444567078219</v>
+      </c>
+      <c r="D45"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="B37" s="40">
-        <f>B33*(1+0.3)*(1+0.3+0.1)</f>
-        <v>57.042384416568858</v>
-      </c>
-      <c r="C37" s="40">
-        <f>C33*(1+0.3)*(1+0.3+0.1)</f>
-        <v>76.619894129909738</v>
-      </c>
-      <c r="D37"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="26" t="s">
+      <c r="B46" s="40">
+        <f>B42*(1+0.3)*(1+0.3+0.1)</f>
+        <v>63.912022393909517</v>
+      </c>
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="40">
-        <f>B37*0.15</f>
-        <v>8.556357662485329</v>
-      </c>
-      <c r="C38" s="40">
-        <f>C37*0.15</f>
-        <v>11.49298411948646</v>
-      </c>
-      <c r="D38"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="26" t="s">
+      <c r="B47" s="40">
+        <f>B46*0.15</f>
+        <v>9.5868033590864279</v>
+      </c>
+      <c r="D47"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="40">
-        <f>B37+B38</f>
-        <v>65.59874207905419</v>
-      </c>
-      <c r="C39" s="40">
-        <f>C37+C38</f>
-        <v>88.112878249396204</v>
-      </c>
-      <c r="D39"/>
-      <c r="O39" s="44"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="26" t="s">
+      <c r="B48" s="40">
+        <f>B46+B47</f>
+        <v>73.498825752995941</v>
+      </c>
+      <c r="D48"/>
+      <c r="N48" s="43"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="40">
+      <c r="B49" s="40">
         <v>25</v>
       </c>
-      <c r="C40" s="40">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="26" t="s">
+      <c r="C49" s="31"/>
+      <c r="D49"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="40">
+      <c r="B50" s="40">
         <v>0.12</v>
       </c>
-      <c r="C41" s="40">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="26" t="s">
+      <c r="C50" s="31"/>
+      <c r="D50"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B42" s="40">
-        <f>(B41*((1+B41)^B40))/(((1+B41)^B40)-1)</f>
+      <c r="B51" s="40">
+        <f>(B50*((1+B50)^B49))/(((1+B50)^B49)-1)</f>
         <v>0.12749996980950773</v>
       </c>
-      <c r="C42" s="40">
-        <f>(C41*((1+C41)^C40))/(((1+C41)^C40)-1)</f>
-        <v>0.12749996980950773</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="26" t="s">
+      <c r="C51" s="31"/>
+      <c r="D51"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B43" s="40">
-        <f>B42*B39</f>
-        <v>8.3638376346210936</v>
-      </c>
-      <c r="C43" s="40">
-        <f>C42*C39</f>
-        <v>11.234389316626846</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="25" t="s">
+      <c r="B52" s="40">
+        <f>B51*B48</f>
+        <v>9.3710980645412523</v>
+      </c>
+      <c r="C52" s="31"/>
+      <c r="D52"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B44" s="19">
-        <f>B43</f>
-        <v>8.3638376346210936</v>
-      </c>
-      <c r="C44" s="19">
-        <f>C43</f>
-        <v>11.234389316626846</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B53" s="19">
+        <f>B52</f>
+        <v>9.3710980645412523</v>
+      </c>
+      <c r="C53" s="31"/>
+      <c r="D53"/>
+    </row>
     <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A31:H31"/>
     <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A28:H28"/>
   </mergeCells>
-  <conditionalFormatting sqref="I17">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThanOrEqual">
-      <formula>1000</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I18:I19">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="I17:I25">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThanOrEqual">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1965,347 +2268,198 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A3:G20"/>
+  <dimension ref="A3:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="54">
-        <v>2019</v>
-      </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="E3" s="54">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="55">
         <v>2022</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="36" t="s">
         <v>65</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="E5" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="10">
         <f>50000*9*9/1000000</f>
         <v>4.05</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="10">
-        <f>50000*9*9/1000000</f>
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>63</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>64</v>
       </c>
       <c r="C7" s="21">
         <f>0.25*C6</f>
         <v>1.0125</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="21">
-        <f>0.25*G6</f>
-        <v>1.0125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>68</v>
       </c>
       <c r="C8" s="21">
         <f>0.45*(C6+C7)</f>
         <v>2.2781250000000002</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="21">
-        <f>0.45*(G6+G7)</f>
-        <v>2.2781250000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="48"/>
-      <c r="B9" s="50"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="49"/>
+      <c r="B9" s="51"/>
       <c r="C9" s="17">
         <f>SUM(C6:C8)</f>
         <v>7.3406250000000002</v>
       </c>
-      <c r="E9" s="48"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="17">
-        <f>SUM(G6:G8)</f>
-        <v>7.3406250000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="54" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="E10" s="54" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="C11" s="23">
-        <f>0.03*CAPEX!B33</f>
-        <v>0.94025908378959633</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="23">
-        <f>0.03*CAPEX!C33</f>
-        <v>1.262965287855655</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="54"/>
-      <c r="B12" s="54"/>
+        <f>0.03*CAPEX!B42</f>
+        <v>1.053494874624882</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="55"/>
+      <c r="B12" s="55"/>
       <c r="C12" s="29">
         <f>C11</f>
-        <v>0.94025908378959633</v>
-      </c>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="29">
-        <f>G11</f>
-        <v>1.262965287855655</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="48" t="s">
+        <v>1.053494874624882</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="50"/>
+      <c r="C13" s="51"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="E13" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="49"/>
-      <c r="G13" s="50"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>72</v>
-      </c>
       <c r="B14" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" s="21">
         <f>0.65*(C6+C7+C8+C11)</f>
-        <v>5.3825746544632374</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="10" t="s">
+        <v>5.4561779185061736</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="21">
-        <f>0.65*(G6+G7+G8+G11)</f>
-        <v>5.5923336871061755</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>75</v>
-      </c>
       <c r="B15" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C15" s="21">
-        <f>0.02*(CAPEX!B33+CAPEX!B34)</f>
-        <v>0.81489120595098363</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="21">
-        <f>0.02*(CAPEX!C33+CAPEX!C34)</f>
-        <v>1.0945699161415676</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="54"/>
-      <c r="B16" s="54"/>
+        <f>0.02*(CAPEX!B42+CAPEX!B43)</f>
+        <v>0.91302889134156429</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="55"/>
+      <c r="B16" s="55"/>
       <c r="C16" s="29">
         <f>SUM(C14:C15)</f>
-        <v>6.197465860414221</v>
-      </c>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="29">
-        <f>SUM(G14:G15)</f>
-        <v>6.6869036032477434</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="48" t="s">
+        <v>6.3692068098477375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="50"/>
+      <c r="C17" s="51"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="49"/>
-      <c r="C17" s="50"/>
-      <c r="E17" s="48" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="49"/>
-      <c r="G17" s="50"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="B18" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>80</v>
-      </c>
       <c r="C18" s="23">
-        <f>0.06*CAPEX!B38</f>
-        <v>0.51338145974911975</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G18" s="23">
-        <f>0.06*CAPEX!C38</f>
-        <v>0.68957904716918761</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="54"/>
-      <c r="B19" s="54"/>
+        <f>0.06*CAPEX!B47</f>
+        <v>0.5752082015451857</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="55"/>
+      <c r="B19" s="55"/>
       <c r="C19" s="17">
         <f>C18</f>
-        <v>0.51338145974911975</v>
-      </c>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="17">
-        <f>G18</f>
-        <v>0.68957904716918761</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" s="50"/>
+        <v>0.5752082015451857</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="51"/>
       <c r="C20" s="17">
         <f>C9+C12+C16+C19</f>
-        <v>14.991731403952937</v>
-      </c>
-      <c r="E20" s="48" t="s">
-        <v>83</v>
-      </c>
-      <c r="F20" s="50"/>
-      <c r="G20" s="17">
-        <f>G9+G12+G16+G19</f>
-        <v>15.980072938272587</v>
+        <v>15.338534886017806</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E19:F19"/>
+  <mergeCells count="10">
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2314,23 +2468,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:K18"/>
+  <dimension ref="B2:G18"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="11"/>
-    <col min="2" max="2" width="19.85546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="11" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="11"/>
+    <col min="2" max="2" width="21.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
         <v>23</v>
       </c>
@@ -2341,33 +2494,24 @@
         <v>30</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>31</v>
@@ -2375,111 +2519,70 @@
       <c r="D5" s="23">
         <v>0</v>
       </c>
-      <c r="E5" s="43">
-        <f>123.25*C17/C16</f>
-        <v>124.14918753108937</v>
+      <c r="E5" s="42">
+        <v>0</v>
       </c>
       <c r="F5" s="42">
-        <f>E5*C18/C17</f>
-        <v>166.75841485657438</v>
-      </c>
-      <c r="G5" s="42">
         <f>D5*E5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="42">
-        <f>D5*F5</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="11">
-        <f>G5/Summary!$C$23</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="11">
-        <f>H5/Summary!$C$23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="27">
-        <f>36320.0422825098/1000</f>
-        <v>36.320042282509796</v>
+        <f>36320.0422893221*0.001</f>
+        <v>36.320042289322096</v>
       </c>
       <c r="E6" s="42">
-        <v>465.07</v>
+        <v>728.17</v>
       </c>
       <c r="F6" s="42">
-        <v>728.17</v>
-      </c>
-      <c r="G6" s="42">
         <f>D6*E6</f>
-        <v>16891.36206432683</v>
-      </c>
-      <c r="H6" s="42">
-        <f>D6*F6</f>
-        <v>26447.165188855157</v>
-      </c>
-      <c r="I6" s="11">
-        <f>G6/Summary!$C$23</f>
-        <v>0.45043751066092319</v>
-      </c>
-      <c r="J6" s="11">
-        <f>H6/Summary!$C$23</f>
-        <v>0.70525959992681631</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+        <v>26447.165193815668</v>
+      </c>
+      <c r="G6" s="11">
+        <f>F6/Summary!$C$23</f>
+        <v>0.70526625898807838</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="41" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="27">
-        <f>36320.0422825098/1000</f>
-        <v>36.320042282509796</v>
+        <f>36320.0422893221*0.001</f>
+        <v>36.320042289322096</v>
       </c>
       <c r="E7" s="42">
-        <v>1313.2</v>
+        <v>1366.03</v>
       </c>
       <c r="F7" s="42">
-        <v>1366.03</v>
-      </c>
-      <c r="G7" s="42">
         <f>D7*E7</f>
-        <v>47695.479525391864</v>
-      </c>
-      <c r="H7" s="42">
-        <f>D7*F7</f>
-        <v>49614.267359176854</v>
-      </c>
-      <c r="I7" s="11">
-        <f>G7/Summary!$C$23</f>
-        <v>1.2718828111895508</v>
-      </c>
-      <c r="J7" s="11">
-        <f>H7/Summary!$C$23</f>
-        <v>1.3230506218163738</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+        <v>49614.267368482659</v>
+      </c>
+      <c r="G7" s="11">
+        <f>F7/Summary!$C$23</f>
+        <v>1.3230631140605693</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>24</v>
       </c>
@@ -2487,67 +2590,46 @@
         <v>32</v>
       </c>
       <c r="D9" s="9">
-        <f>198825004.077851/1000000</f>
-        <v>198.82500407785099</v>
-      </c>
-      <c r="E9" s="40">
-        <v>0.38</v>
+        <f>729433625.357823/10^6</f>
+        <v>729.43362535782296</v>
+      </c>
+      <c r="E9" s="48">
+        <f>0.38*C18/C17</f>
+        <v>0.51041975308641974</v>
       </c>
       <c r="F9" s="42">
-        <f>E9*C18/C17</f>
-        <v>0.51041975308641974</v>
-      </c>
-      <c r="G9" s="42">
         <f>D9*E9</f>
-        <v>75.553501549583373</v>
-      </c>
-      <c r="H9" s="42">
-        <f>D9*F9</f>
-        <v>101.4842094888231</v>
-      </c>
-      <c r="I9" s="11">
-        <f>G9/Summary!$C$23</f>
-        <v>2.0147653593657554E-3</v>
-      </c>
-      <c r="J9" s="11">
-        <f>H9/Summary!$C$23</f>
-        <v>2.7062527296172123E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>31</v>
+        <v>372.31733094807197</v>
+      </c>
+      <c r="G9" s="11">
+        <f>F9/Summary!$C$23</f>
+        <v>9.928582108133641E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="D10" s="9">
-        <v>0</v>
-      </c>
-      <c r="E10" s="40">
-        <v>67.83</v>
+        <f>21479811.9998673/10^6</f>
+        <v>21.479811999867302</v>
+      </c>
+      <c r="E10" s="48">
+        <v>256</v>
       </c>
       <c r="F10" s="42">
-        <v>288.06</v>
-      </c>
-      <c r="G10" s="42">
         <f>D10*E10</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="42">
-        <f>D10*F10</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="11">
-        <f>G10/Summary!$C$23</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="11">
-        <f>H10/Summary!$C$23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+        <v>5498.8318719660292</v>
+      </c>
+      <c r="G10" s="11">
+        <f>F10/Summary!$C$23</f>
+        <v>0.14663728814507299</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>25</v>
       </c>
@@ -2555,93 +2637,68 @@
         <v>33</v>
       </c>
       <c r="D11" s="31">
-        <v>2467.5911550000001</v>
-      </c>
-      <c r="E11" s="40">
-        <v>6.7830000000000001E-2</v>
-      </c>
-      <c r="F11" s="40">
-        <v>8.5300000000000001E-2</v>
-      </c>
-      <c r="G11" s="42">
+        <v>2467.6098790000001</v>
+      </c>
+      <c r="E11" s="48">
+        <f>69.6*C18/C17/1000</f>
+        <v>9.3487407407407408E-2</v>
+      </c>
+      <c r="F11" s="42">
         <f>D11*E11</f>
-        <v>167.37670804365001</v>
-      </c>
-      <c r="H11" s="42">
-        <f>D11*F11</f>
-        <v>210.48552552149999</v>
-      </c>
-      <c r="I11" s="11">
-        <f>G11/Summary!$C$23</f>
-        <v>4.4633906624395392E-3</v>
-      </c>
-      <c r="J11" s="11">
-        <f>H11/Summary!$C$23</f>
-        <v>5.6129621628496634E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+        <v>230.6904500806163</v>
+      </c>
+      <c r="G11" s="11">
+        <f>F11/Summary!$C$23</f>
+        <v>6.1518196570525905E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>37</v>
       </c>
       <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19">
-        <f>(G5+G6+G9+G10+G11)/1000000*8000</f>
-        <v>137.07433819136051</v>
-      </c>
-      <c r="H12" s="19">
-        <f>(H5+H6+H9+H10+H11)/1000000*8000</f>
-        <v>214.07307939092385</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E12" s="19"/>
+      <c r="F12" s="19">
+        <f>(F5+F6+F9+F10+F11)/1000000*8000</f>
+        <v>260.39203877448313</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="36" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>37</v>
       </c>
       <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19">
-        <f>(G5+G7+G9+G10+G11)/1000000*8000</f>
-        <v>383.5072778798808</v>
-      </c>
-      <c r="H13" s="19">
-        <f>(H5+H7+H9+H10+H11)/1000000*8000</f>
-        <v>399.40989675349743</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E13" s="19"/>
+      <c r="F13" s="19">
+        <f>(F5+F7+F9+F10+F11)/1000000*8000</f>
+        <v>445.72885617181902</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
       <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="K15"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" s="23">
         <v>603.1</v>
@@ -2657,7 +2714,7 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C18" s="21">
         <v>816</v>
@@ -2665,8 +2722,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2675,735 +2732,375 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B2:L31"/>
+  <dimension ref="B2:F24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="E2" s="54" t="s">
-        <v>101</v>
-      </c>
-      <c r="F2" s="54"/>
-      <c r="H2" s="54" t="s">
-        <v>112</v>
-      </c>
-      <c r="I2" s="54"/>
-      <c r="K2" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="L2" s="54"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="E2" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="55"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="C3" s="21">
-        <f>SUM(CAPEX!B29)</f>
-        <v>8.3802057378751886</v>
+        <f>CAPEX!B39</f>
+        <v>9.3894373852485007</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F3" s="21">
-        <f>CAPEX!B30</f>
-        <v>11.256375114578029</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="I3" s="21">
-        <f t="shared" ref="I3:I18" si="0">C3</f>
-        <v>8.3802057378751886</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="L3" s="21">
-        <f t="shared" ref="L3:L18" si="1">F3</f>
-        <v>11.256375114578029</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+        <f t="shared" ref="F3:F18" si="0">C3</f>
+        <v>9.3894373852485007</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C4" s="21">
-        <f>SUM(CAPEX!B33)</f>
-        <v>31.341969459653214</v>
+        <f>CAPEX!B42</f>
+        <v>35.1164958208294</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>54</v>
       </c>
       <c r="F4" s="21">
-        <f>CAPEX!C33</f>
-        <v>42.098842928521833</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="21">
         <f t="shared" si="0"/>
-        <v>31.341969459653214</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" s="21">
-        <f t="shared" si="1"/>
-        <v>42.098842928521833</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+        <v>35.1164958208294</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C5" s="21">
-        <f>SUM(CAPEX!B34)</f>
-        <v>9.4025908378959642</v>
+        <f>CAPEX!B43</f>
+        <v>10.534948746248819</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="21">
-        <f>CAPEX!C34</f>
-        <v>12.62965287855655</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="21">
         <f t="shared" si="0"/>
-        <v>9.4025908378959642</v>
-      </c>
-      <c r="K5" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" s="21">
-        <f t="shared" si="1"/>
-        <v>12.62965287855655</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+        <v>10.534948746248819</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" s="21">
-        <f>SUM(CAPEX!B35)</f>
-        <v>12.223368089264753</v>
+        <f>CAPEX!B44</f>
+        <v>13.695433370123464</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F6" s="21">
-        <f>CAPEX!C35</f>
-        <v>16.418548742123512</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6" s="21">
         <f t="shared" si="0"/>
-        <v>12.223368089264753</v>
-      </c>
-      <c r="K6" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="L6" s="21">
-        <f t="shared" si="1"/>
-        <v>16.418548742123512</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+        <v>13.695433370123464</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C7" s="21">
-        <f>SUM(CAPEX!B36)</f>
-        <v>4.0744560297549182</v>
+        <f>CAPEX!B45</f>
+        <v>4.5651444567078219</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>57</v>
       </c>
       <c r="F7" s="21">
-        <f>CAPEX!C36</f>
-        <v>5.4728495807078383</v>
-      </c>
-      <c r="H7" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="21">
         <f t="shared" si="0"/>
-        <v>4.0744560297549182</v>
-      </c>
-      <c r="K7" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="L7" s="21">
-        <f t="shared" si="1"/>
-        <v>5.4728495807078383</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+        <v>4.5651444567078219</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C8" s="21">
-        <f>SUM(CAPEX!B37)</f>
-        <v>57.042384416568858</v>
+        <f>CAPEX!B46</f>
+        <v>63.912022393909517</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>58</v>
       </c>
       <c r="F8" s="21">
-        <f>CAPEX!C37</f>
-        <v>76.619894129909738</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" s="21">
         <f t="shared" si="0"/>
-        <v>57.042384416568858</v>
-      </c>
-      <c r="K8" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="21">
-        <f t="shared" si="1"/>
-        <v>76.619894129909738</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+        <v>63.912022393909517</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C9" s="21">
-        <f>SUM(CAPEX!B38)</f>
-        <v>8.556357662485329</v>
+        <f>CAPEX!B47</f>
+        <v>9.5868033590864279</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>61</v>
       </c>
       <c r="F9" s="21">
-        <f>CAPEX!C38</f>
-        <v>11.49298411948646</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="I9" s="21">
         <f t="shared" si="0"/>
-        <v>8.556357662485329</v>
-      </c>
-      <c r="K9" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" s="21">
-        <f t="shared" si="1"/>
-        <v>11.49298411948646</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+        <v>9.5868033590864279</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="21">
-        <f>SUM(CAPEX!B39)</f>
-        <v>65.59874207905419</v>
+        <f>CAPEX!B48</f>
+        <v>73.498825752995941</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>59</v>
       </c>
       <c r="F10" s="21">
-        <f>CAPEX!C39</f>
-        <v>88.112878249396204</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I10" s="21">
         <f t="shared" si="0"/>
-        <v>65.59874207905419</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="L10" s="21">
-        <f t="shared" si="1"/>
-        <v>88.112878249396204</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+        <v>73.498825752995941</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" s="21">
+        <f>SUM('Production costs'!B9)</f>
         <v>0</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F11" s="21">
-        <f>SUM('Production costs'!F9)</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="I11" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="10" t="s">
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="L11" s="21">
-        <f t="shared" si="1"/>
+      <c r="C12" s="21">
+        <f>SUM('Production costs'!B12)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0</v>
-      </c>
       <c r="E12" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F12" s="21">
-        <f>SUM('Production costs'!F12)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I12" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K12" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="L12" s="21">
-        <f t="shared" si="1"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="21">
+        <f>SUM('Production costs'!B16)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="21">
-        <v>0</v>
-      </c>
       <c r="E13" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F13" s="21">
-        <f>SUM('Production costs'!F16)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I13" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="L13" s="21">
-        <f t="shared" si="1"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="21">
+        <f>SUM('Production costs'!B19)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="21">
-        <v>0</v>
-      </c>
       <c r="E14" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F14" s="21">
-        <f>SUM('Production costs'!F19)</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="I14" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="L14" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="21">
-        <f>SUM(CAPEX!B40)</f>
         <v>25</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="21">
-        <v>25</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="21">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="K15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="21">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="21">
-        <f>SUM(CAPEX!B41)</f>
         <v>0.12</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="21">
-        <v>0.12</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="21">
         <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
-      <c r="K16" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" s="21">
-        <f t="shared" si="1"/>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C17" s="20">
-        <f>SUM(CAPEX!B42)</f>
         <v>0.12749996980950773</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>28</v>
       </c>
       <c r="F17" s="20">
-        <v>0.12749996980950773</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="20">
         <f t="shared" si="0"/>
         <v>0.12749996980950773</v>
       </c>
-      <c r="K17" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="L17" s="20">
-        <f t="shared" si="1"/>
-        <v>0.12749996980950773</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
         <v>36</v>
       </c>
       <c r="C18" s="17">
-        <f>SUM(CAPEX!B44)</f>
-        <v>8.3638376346210936</v>
+        <f>CAPEX!B53</f>
+        <v>9.3710980645412523</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>36</v>
       </c>
       <c r="F18" s="17">
-        <f>CAPEX!C44</f>
-        <v>11.234389316626846</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" s="17">
         <f t="shared" si="0"/>
-        <v>8.3638376346210936</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" s="17">
-        <f t="shared" si="1"/>
-        <v>11.234389316626846</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+        <v>9.3710980645412523</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F19" s="17">
         <v>0</v>
       </c>
-      <c r="H19" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="I19" s="17">
-        <v>0</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="L19" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C20" s="17">
-        <f>OPEX!G12</f>
-        <v>137.07433819136051</v>
+        <f>OPEX!F12</f>
+        <v>260.39203877448313</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F20" s="17">
-        <f>OPEX!H12</f>
-        <v>214.07307939092385</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="I20" s="17">
-        <f>OPEX!G13</f>
-        <v>383.5072778798808</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="L20" s="17">
-        <f>OPEX!H13</f>
-        <v>399.40989675349743</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+        <f>OPEX!F13</f>
+        <v>445.72885617181902</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C21" s="17">
         <f>(C18+C19+C20)</f>
-        <v>145.4381758259816</v>
+        <v>269.76313683902436</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F21" s="17">
         <f>(F18+F19+F20)</f>
-        <v>225.3074687075507</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="I21" s="17">
-        <f>(I18+I19+I20)</f>
-        <v>391.87111551450192</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="L21" s="17">
-        <f>(L18+L19+L20)</f>
-        <v>410.64428607012428</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+        <v>455.09995423636025</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C22" s="17">
         <f>(C21)*1000000/8000</f>
-        <v>18179.771978247703</v>
+        <v>33720.392104878047</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F22" s="17">
         <f>(F21)*1000000/8000</f>
-        <v>28163.433588443837</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="I22" s="17">
-        <f>(I21)*1000000/8000</f>
-        <v>48983.889439312741</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="L22" s="17">
-        <f>(L21)*1000000/8000</f>
-        <v>51330.535758765531</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+        <v>56887.494279545033</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C23" s="17">
-        <v>37499.901017440301</v>
+        <v>37499.546953745201</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F23" s="17">
         <f>C23</f>
-        <v>37499.901017440301</v>
-      </c>
-      <c r="H23" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="I23" s="17">
-        <f>F23</f>
-        <v>37499.901017440301</v>
-      </c>
-      <c r="K23" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="L23" s="17">
-        <f>I23</f>
-        <v>37499.901017440301</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+        <v>37499.546953745201</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="C24" s="45">
+        <v>109</v>
+      </c>
+      <c r="C24" s="44">
         <f>C22/C23</f>
-        <v>0.48479519905379825</v>
+        <v>0.89922131983277953</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="F24" s="45">
+        <v>109</v>
+      </c>
+      <c r="F24" s="44">
         <f>F22/F23</f>
-        <v>0.75102687805351009</v>
-      </c>
-      <c r="H24" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="I24" s="45">
-        <f>I22/I23</f>
-        <v>1.3062404995824259</v>
-      </c>
-      <c r="K24" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="L24" s="45">
-        <f>L22/L23</f>
-        <v>1.3688178999430674</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F26" s="55">
-        <f>OPEX!H6/Summary!F23</f>
-        <v>0.70525959992681631</v>
-      </c>
-      <c r="I26">
-        <f>I18*10^6/8000/I23</f>
-        <v>2.7879532371069705E-2</v>
-      </c>
-      <c r="L26">
-        <f>L18*10^6/8000/L23</f>
-        <v>3.744806323422694E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F27" s="55">
-        <f>OPEX!H7/Summary!F23</f>
-        <v>1.3230506218163738</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F28" s="55">
-        <f>OPEX!H9/Summary!F23</f>
-        <v>2.7062527296172123E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F29" s="55">
-        <f>OPEX!H10/Summary!F23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F30" s="55">
-        <f>OPEX!H11/Summary!F23</f>
-        <v>5.6129621628496634E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="F31" s="55">
-        <f>F18*10^6/8000/F23</f>
-        <v>3.744806323422694E-2</v>
+        <v>1.5170181749052702</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
